--- a/AAII_Financials/Quarterly/CCEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -656,440 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45743</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45379</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44470</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44379</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43644</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43371</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43280</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43189</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43007</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6133600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6179600</v>
+      </c>
+      <c r="F8" s="3">
         <v>6238700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6234300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6018700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5545100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5492300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5916800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5265200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5307800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5153600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4934900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4900100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4876700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4830600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8478100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4284700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>6421000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2469300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5889000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3245100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5020300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7017400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3705700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6773300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3286900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3934300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3656800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2633900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2922900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>3325600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>3426600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2672600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3965900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3995600</v>
+      </c>
+      <c r="F9" s="3">
         <v>4004900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4002100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3891600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3585400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3538200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3811600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3385800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3413300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3244200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3106500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3111900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3097000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3092900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>5213300</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U9" s="3">
         <v>4162100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W9" s="3">
         <v>3716700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="3">
         <v>3288100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4319900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="3">
         <v>4200300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2036300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2379200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2208200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1628200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1841300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1990400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2079000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1647100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2167700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2183900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2233800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2232200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2127100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1959700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1954100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2105200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1879400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1894600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1909500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1828400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1788200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1779700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1737700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3264800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U10" s="3">
         <v>2259000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="3">
         <v>2172300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1732300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2697400</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2573000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1250500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1555100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1448600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1005700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1081500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1335200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1347500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1025500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1124,8 +1149,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1249,14 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,154 +1353,166 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>17000</v>
+        <v>-12000</v>
       </c>
       <c r="E14" s="3">
-        <v>17000</v>
+        <v>-12100</v>
       </c>
       <c r="F14" s="3">
-        <v>-19900</v>
+        <v>18200</v>
       </c>
       <c r="G14" s="3">
-        <v>-18400</v>
+        <v>18200</v>
       </c>
       <c r="H14" s="3">
-        <v>234000</v>
+        <v>-21100</v>
       </c>
       <c r="I14" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>239700</v>
+      </c>
+      <c r="K14" s="3">
         <v>252100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>12300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>12400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>19900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>19100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-15800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-15800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>37900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>14000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>4300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>63300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>3500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>4800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>23300</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>251100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>253000</v>
+      </c>
+      <c r="F15" s="3">
         <v>114500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>114400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>258900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>238600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>110300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>118800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>225000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>226800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>83500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>79900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>205800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>204800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>78600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1516,8 +1561,14 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1600,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5382800</v>
+        <v>5311700</v>
       </c>
       <c r="E17" s="3">
-        <v>5379000</v>
+        <v>5351500</v>
       </c>
       <c r="F17" s="3">
-        <v>5239600</v>
+        <v>5381600</v>
       </c>
       <c r="G17" s="3">
-        <v>4827300</v>
+        <v>5377800</v>
       </c>
       <c r="H17" s="3">
-        <v>4745800</v>
+        <v>5240800</v>
       </c>
       <c r="I17" s="3">
+        <v>4828400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4740100</v>
+      </c>
+      <c r="K17" s="3">
         <v>5112600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4641100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4678700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4487700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4297200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4277300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4256800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4194700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7401700</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U17" s="3">
         <v>5856800</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W17" s="3">
         <v>5332700</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="3">
         <v>4742200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6089200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="3">
         <v>5925800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3058600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3335000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3156800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2426800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2705500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2846500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2959800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2426900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>855900</v>
+        <v>821900</v>
       </c>
       <c r="E18" s="3">
-        <v>855300</v>
+        <v>828100</v>
       </c>
       <c r="F18" s="3">
-        <v>779100</v>
+        <v>857100</v>
       </c>
       <c r="G18" s="3">
-        <v>717800</v>
+        <v>856500</v>
       </c>
       <c r="H18" s="3">
-        <v>746500</v>
+        <v>778000</v>
       </c>
       <c r="I18" s="3">
+        <v>716800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>752100</v>
+      </c>
+      <c r="K18" s="3">
         <v>804100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>624100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>629200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>666000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>637700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>622800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>619800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>635900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1076400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U18" s="3">
         <v>564200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W18" s="3">
         <v>556300</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="3">
         <v>278200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>928100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="3">
         <v>847500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>228200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>599300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>500000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>207100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>217400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>479100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>466700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>245700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,252 +1846,266 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>14100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>14100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>5400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>8500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>7500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-74600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U20" s="3">
         <v>-70500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W20" s="3">
         <v>-62300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-59200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-51900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-28700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-23300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>956300</v>
+        <v>1071800</v>
       </c>
       <c r="E21" s="3">
-        <v>955600</v>
+        <v>1079900</v>
       </c>
       <c r="F21" s="3">
-        <v>1034600</v>
+        <v>957500</v>
       </c>
       <c r="G21" s="3">
-        <v>953200</v>
+        <v>956800</v>
       </c>
       <c r="H21" s="3">
-        <v>852600</v>
+        <v>1033400</v>
       </c>
       <c r="I21" s="3">
+        <v>952100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>858300</v>
+      </c>
+      <c r="K21" s="3">
         <v>918500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>843800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>850600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>740600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>709100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>825300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>821400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>707000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>864700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>1243100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1158100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>352900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>722500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>624400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>322300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>317300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>591300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>561000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>373600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>85300</v>
+      </c>
+      <c r="F22" s="3">
         <v>96900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>96800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>77300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>71200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>69400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>74700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>69100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>69700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>47000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>45000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>51300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>51100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>44400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -2075,204 +2154,222 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>765800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>771600</v>
+      </c>
+      <c r="F23" s="3">
         <v>768500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>767900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>738100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>680100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>461200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>496900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>559800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>564400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>609000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>583200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>601000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>598100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>565900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1001800</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U23" s="3">
         <v>493700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W23" s="3">
         <v>494100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="3">
         <v>219000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>876200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="3">
         <v>791500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>196500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>571800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>471300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>183900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>195400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>445400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>436500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>218800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>200500</v>
+      </c>
+      <c r="F24" s="3">
         <v>156700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>156600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>189200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>174300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>133600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>143900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>125400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>126400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>158600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>151900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>134800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>134200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>113800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>199900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U24" s="3">
         <v>226800</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W24" s="3">
         <v>114300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="3">
         <v>88200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>219000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB24" s="3">
         <v>198500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>70600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>143500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>120800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>46500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-88900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>104300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>102100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2466,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>566800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>571000</v>
+      </c>
+      <c r="F26" s="3">
         <v>611700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>611300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>548900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>505700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>327700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>353000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>434500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>438000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>450400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>431300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>466200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>463900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>452100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>801900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U26" s="3">
         <v>266900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W26" s="3">
         <v>379700</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y26" s="3">
         <v>130800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>657100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB26" s="3">
         <v>593000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>125900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>428200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>350500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>137300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>284400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>341100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>334400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>164900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>553100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F27" s="3">
         <v>604100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>603700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>534900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>492800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>321500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>346300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>427000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>430400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>450400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>431300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>466200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>463900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>449400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>797600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U27" s="3">
         <v>264700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W27" s="3">
         <v>379700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y27" s="3">
         <v>130800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>657100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB27" s="3">
         <v>593000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>125900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>428200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>350500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>137300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>284400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>341100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>334400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>164900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2778,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2719,11 +2840,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2737,32 +2858,38 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>31800</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-351400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2986,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,204 +3090,222 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-14100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-14100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-5400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-8500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>74600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U32" s="3">
         <v>70500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W32" s="3">
         <v>62300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y32" s="3">
         <v>59200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>51900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB32" s="3">
         <v>56000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>31800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>27500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>28700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>23300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>22000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>33700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>30300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>553100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F33" s="3">
         <v>604100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>603700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>534900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>492800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>321500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>346300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>427000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>430400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>450400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>431300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>466200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>463900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>449400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>797600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U33" s="3">
         <v>264700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W33" s="3">
         <v>379700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="3">
         <v>130800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>657100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB33" s="3">
         <v>593000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>157600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>428200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>350500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>137300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>341100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>334400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>164900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3402,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>553100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F35" s="3">
         <v>604100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>603700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>534900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>492800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>321500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>346300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>427000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>430400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>450400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>431300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>466200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>463900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>449400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>797600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U35" s="3">
         <v>264700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W35" s="3">
         <v>379700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y35" s="3">
         <v>130800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>657100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB35" s="3">
         <v>593000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>157600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>428200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>350500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>137300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>341100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>334400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>164900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46115</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45743</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45379</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44470</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44379</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43644</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43371</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43280</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43189</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43007</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3657,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,154 +3695,162 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2005300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2020300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1077800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1077100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1943800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1790800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1618200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1743300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1725100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1739000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1568500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1501900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1214000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1208200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1482300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1645900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1652500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>968900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>340300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>322600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>389900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>320700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>356800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB41" s="3">
         <v>446000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>363500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>581400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>440200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>271400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>395300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>530700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>343300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>408400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>275700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>277700</v>
+      </c>
+      <c r="F42" s="3">
         <v>63400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>63400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>469800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>432900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>155300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>167300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>291400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>293800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>679800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>650900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>941000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>936500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>377300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3687,11 +3866,11 @@
       <c r="W42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3720,448 +3899,478 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4054000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4084400</v>
+      </c>
+      <c r="F43" s="3">
         <v>3878100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3875400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3991800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3677700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3071700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3309200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3361200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3388400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3259600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3121300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3349300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3333300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3194400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1737800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1744700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2044100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1930900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1830300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2139600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1850600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2024500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB43" s="3">
         <v>2446900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2097500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2356500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2503600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>2059000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2011500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2301200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>2552500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>2164300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2190600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2207000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1816400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1815100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2118300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1951600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1664800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1793400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2050800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2067400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1498800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1435200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1871200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1862200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1474800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>736000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>738900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>862600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>778600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>738000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>964700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>719300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>816300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB44" s="3">
         <v>1103200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>815200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>893600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>974900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>857300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>713700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>847100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>899800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>814600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>990600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>998000</v>
+      </c>
+      <c r="F45" s="3">
         <v>119800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>119700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>940800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>866800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>153200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>165100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>626800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>631900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>150300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>143900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>766400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>762700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>271500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>285300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>286400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>244100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>291800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>276600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>245000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>213800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>306000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>280200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>242300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>636400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>620800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>522800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>518300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>526200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>499300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>467900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9516100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9587400</v>
+      </c>
+      <c r="F46" s="3">
         <v>7137500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7132500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9464600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8719800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6872300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7403500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8055300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8120500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7300800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6990900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8141900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8103000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6992600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4404900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4422500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4119700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3341600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3167500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3739200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3104400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3503600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB46" s="3">
         <v>4276200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3518600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4467800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4539600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3638800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4205200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4295000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3855200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>93900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>93900</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>138700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>149500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>111600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>106900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>205200</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
@@ -4210,204 +4419,222 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7096800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7149900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7226700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7221600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7263000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6691500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6661100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7176000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6838100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6893500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5906900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5656200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5542600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5516100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5558400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4171500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4188100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4372600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4528400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4292500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>4271000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>4035400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>4747900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB48" s="3">
         <v>4884400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>4573800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>4521600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>4537200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>4194500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>4213000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>4196200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>4227700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>4431900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19820400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>19968900</v>
+      </c>
+      <c r="F49" s="3">
         <v>19990600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>19976500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>19892200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>18326900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>18051600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>19446800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>18943500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>19097000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>18690200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>17896900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>18342800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>18255100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>18280400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>11813100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>11860100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>11836300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>11873900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>11255300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>11140000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>11315200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>12449500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB49" s="3">
         <v>12739900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>12825100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>13029000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>13019400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>12083900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>11972600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>12247600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>12254400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>12072600</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4731,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,106 +4835,118 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>720700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>726100</v>
+      </c>
+      <c r="F52" s="3">
         <v>618800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>618300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>601100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>553800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>449300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>484100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>557200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>561700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>325000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>311200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>465100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>462800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>268200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>399900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>401500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>354800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>378000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>358300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>336900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>451500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>396300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB52" s="3">
         <v>385200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>511700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>181800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>175800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>149500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>152600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>370300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>359000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>440900</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,106 +5043,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37155100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>37433400</v>
+      </c>
+      <c r="F54" s="3">
         <v>35073400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>35048700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>37241900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>34311300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>32198000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>34686600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>34395200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>34673800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>32335600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>30963200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>32527300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>32371800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>31327300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>20789400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>20872100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>20683400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>20121900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>19073600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>19487100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>18906400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>21097200</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB54" s="3">
         <v>22285900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>21429300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>22200300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>22272000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>20138400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>19977000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>21019400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>21136000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>20800600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5189,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,596 +5227,634 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8042800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8103000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3551700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3549200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7929700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7305700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3137000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3379400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6756700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6811400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2834100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2713800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5978200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5949600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2892000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2976200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2988100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2926200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2999200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2842900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3144100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2935200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3144500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB57" s="3">
         <v>3595600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3326900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3725000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3366100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2656000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2781200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2886900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2898100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2615400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1902300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1916600</v>
+      </c>
+      <c r="F58" s="3">
         <v>551800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>551400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2644400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2436300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1440100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1551400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2165400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2183000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1436900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1376000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2647400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2634700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1427800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>870000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>873400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>826800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>860400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>815600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>632900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>509600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>902200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB58" s="3">
         <v>723800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>577600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>110100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>472500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>436400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>300900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1009800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1206100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>981700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>759500</v>
+      </c>
+      <c r="F59" s="3">
         <v>1153000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1152200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>768600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>708100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1018700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1097500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>582900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>587600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>888700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>851000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>935600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>931100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>769500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>627900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>630400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>610900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>571800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>542000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>662500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>490900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>599600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB59" s="3">
         <v>757600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>556400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>576600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>611300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>515000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>527000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>527300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>536300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>511600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10706900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10787100</v>
+      </c>
+      <c r="F60" s="3">
         <v>8905700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8899400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11350900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10457700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8436700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9088800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9512500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9589500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8044700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7703200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9569900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>9524100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7815500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4474100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4491900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4363900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4431400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4200600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4439500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3935700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4646200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB60" s="3">
         <v>5077100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4460900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>4411600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4449900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>3607500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>3609100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>4424000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4640600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>4108700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12040700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12130900</v>
+      </c>
+      <c r="F61" s="3">
         <v>12121600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>12113100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11429400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10530000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10410000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11214600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11062900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11152500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11310900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10830900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>10435600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10385700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11480200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6897000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6924500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6882200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6054300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5738900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5794100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5321300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6347800</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>6626200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>6031400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6276500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>6326700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6034200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6010500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>5767000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>5917400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>6222600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>328300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>330800</v>
+      </c>
+      <c r="F62" s="3">
         <v>221900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>221800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>330400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>304400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>249500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>268800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>145700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>146900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>218900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>209600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>165900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>165100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>203100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2907100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2918700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3109600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3006700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2850100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2786800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2836600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3152400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3">
         <v>3187000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3215100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3332600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3325400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3100200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3017300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>3234700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>3195400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>3128100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5951,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +6055,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,106 +6159,118 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27128800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>27332000</v>
+      </c>
+      <c r="F66" s="3">
         <v>25324600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>25306800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>27277100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25130600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22895700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24665400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>24742300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>24942800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>23519400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>22521200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>24055700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>23940700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>23368600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>14278200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14335000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14355600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>13492500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12789600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>13020300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>12093600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14146500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB66" s="3">
         <v>14890300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>13707400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>14020700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>14102000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>12741800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>12636900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>13425700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>13753400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>13459400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6305,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6405,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6509,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6278,8 +6613,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,106 +6717,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10224200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>10300800</v>
+      </c>
+      <c r="F72" s="3">
         <v>10355800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>10348500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>10486200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>9661100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>9112700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9817100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>9340000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9415600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>9098000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>8711900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8745600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>8703800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>7938400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6298300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6323400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6122700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6432300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6097200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6291200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>7222700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6744100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB72" s="3">
         <v>7194700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>8186600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>8006200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>8002600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>7245900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>7195200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>7446600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>7238000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>7203200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6925,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +7029,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,106 +7133,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9469200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9540200</v>
+      </c>
+      <c r="F76" s="3">
         <v>9199200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9192800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9406000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8665800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8788700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9468000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9135300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9209300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8816200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8442000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8471600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8431100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7958700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6511200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>6537100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>6327700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6629400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>6284000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6466800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>6812800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6950700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB76" s="3">
         <v>7395500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>7721900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>8179600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>8170000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7396600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7340100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>7593600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>7382700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>7341200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7341,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46115</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45743</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45379</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44470</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44379</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43644</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43371</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43280</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43189</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43007</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>553100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F81" s="3">
         <v>604100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>603700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>534900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>492800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>321500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>346300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>427000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>430400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>450400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>431300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>466200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>463900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>449400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>797600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U81" s="3">
         <v>264700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W81" s="3">
         <v>379700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y81" s="3">
         <v>130800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>657100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB81" s="3">
         <v>593000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>157600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>428200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>350500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>137300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>341100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>334400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>164900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,106 +7596,114 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>205100</v>
+      </c>
+      <c r="F83" s="3">
         <v>187400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>201900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>192900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>194400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>180200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>164100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>176900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>176000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>196100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>148600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>174700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>185400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>205300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3">
         <v>371100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
         <v>367000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB83" s="3">
         <v>366600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>156500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>150700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>153100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>138500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>121900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>145900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>124500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>154800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7800,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7904,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +8008,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +8112,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8216,118 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>592000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>596400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1154700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1153900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>577600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>532200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1003700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1081300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>601100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>606000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>828500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>793300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>713400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>710000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>683400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U89" s="3">
         <v>985200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="3">
         <v>1196800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB89" s="3">
         <v>985300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>452900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>955800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>717700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>24400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>538000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>743900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>319800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>207600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,106 +8362,114 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-177300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-178600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-238900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-238800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-185100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-207600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-223600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-208900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-210600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-225500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-215900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-144100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-143400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-172100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-134000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-134000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-274000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-298000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-277800</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-303500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-261200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-114800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-125600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-113000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-215200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-101000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-111100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-111100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8566,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,106 +8670,118 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-328300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-330800</v>
+      </c>
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-370800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-341600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-173400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-186800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-869000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-876000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-42000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-40200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-470000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-467700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-226000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
         <v>-5713600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-345500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-342100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-116300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-219600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-106600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-102100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-114400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,56 +8816,58 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>208800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>210300</v>
+      </c>
+      <c r="F96" s="3">
         <v>328800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>328500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>215000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>198100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>293500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>316200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>183800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>185200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>294600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>282100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>168100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>167300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>270900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8417,40 +8884,46 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-320700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-338500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-157600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-151900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-150700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-110900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-114400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-228900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-92000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +9020,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +9124,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,180 +9228,192 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>204600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1576800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1575700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-119500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-110100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-675500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-727700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>177900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>179300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-513400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-491600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-487400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-485100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-663700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U100" s="3">
         <v>5005100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-930400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-558000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-349400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-678200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-434200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-35400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-439200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-449900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-277100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-116700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-6700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>13400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>13500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-8700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-8700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-24600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-22600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>7800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>8300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>21000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U101" s="3">
         <v>49900</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3">
         <v>4500</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-1200</v>
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8928,113 +9425,125 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>477600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>481200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-435000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-434700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>56200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>51800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>148600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>160000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-76600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-77200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>273600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>262000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-252700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-251500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-230800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3">
         <v>326600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-74500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="3">
         <v>85200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-209400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>141200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>148300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-127400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-124100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>187400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-65100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-24700</v>
       </c>
     </row>
